--- a/docs/D-REC RR Checklist_2026-04-02.xlsx
+++ b/docs/D-REC RR Checklist_2026-04-02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://powertrust1-my.sharepoint.com/personal/pbirkelo_powertrust_com/Documents/Supply Management/1) Supply Operations/D-REC Label/2026/D-REC RR Checklist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4ABAAA88-1C54-4127-9805-50D0AD32769B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{01FA3621-879B-4280-B62E-8ADF5A28D3F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" firstSheet="2" activeTab="2" xr2:uid="{1C812538-09BA-6B45-A732-40B0B2B679B5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="251">
   <si>
     <t>#</t>
   </si>
@@ -808,11 +808,54 @@
 (from "All Fields")</t>
   </si>
   <si>
+    <t>Tooltip/explanation needed for registrant</t>
+  </si>
+  <si>
+    <t>How is it Verified? (tooltip for reviewer)</t>
+  </si>
+  <si>
     <t>Cross check with:
 - RMS
 - SLD
 - Proof of Ownership
 - OD letter</t>
+  </si>
+  <si>
+    <t>If public (government) funding has been received when did/will it finish?</t>
+  </si>
+  <si>
+    <t>"Yes" means individual senior review required</t>
+  </si>
+  <si>
+    <t>All items mean individual senior review required</t>
+  </si>
+  <si>
+    <t>"Yes" means facility cannot be approved</t>
+  </si>
+  <si>
+    <t>Individual review may be required depending on response</t>
+  </si>
+  <si>
+    <t>Cross check with:
+- site photos
+- capacity</t>
+  </si>
+  <si>
+    <t>Cross check with:
+- PV system owner
+- Offtaker
+- OD letter
+- RE attributes</t>
+  </si>
+  <si>
+    <t>Cross check with:
+- grid-status
+- export status
+- network meter availability
+- useable data access mode
+- site name
+- SLD
+- meter/measurement IDs</t>
   </si>
 </sst>
 </file>
@@ -4983,7 +5026,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>5</v>
+        <v>240</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>6</v>
@@ -4995,7 +5038,7 @@
         <v>8</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>9</v>
+        <v>241</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>10</v>
@@ -5033,7 +5076,7 @@
         <v>17</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M4" s="8"/>
     </row>
@@ -5073,7 +5116,7 @@
       </c>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="2:13" ht="17.100000000000001">
+    <row r="6" spans="2:13" ht="33.950000000000003">
       <c r="B6" s="3">
         <v>3</v>
       </c>
@@ -5105,7 +5148,7 @@
         <v>17</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="M6" s="8"/>
     </row>
@@ -6152,7 +6195,7 @@
         <v>65</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>136</v>
+        <v>243</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>15</v>
@@ -6171,7 +6214,7 @@
       </c>
       <c r="M36" s="8"/>
     </row>
-    <row r="37" spans="2:13" ht="17.100000000000001">
+    <row r="37" spans="2:13" ht="33.950000000000003">
       <c r="B37" s="3">
         <v>34</v>
       </c>
@@ -6201,11 +6244,11 @@
         <v>17</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>15</v>
+        <v>244</v>
       </c>
       <c r="M37" s="8"/>
     </row>
-    <row r="38" spans="2:13" ht="17.100000000000001">
+    <row r="38" spans="2:13" ht="33.950000000000003">
       <c r="B38" s="3">
         <v>35</v>
       </c>
@@ -6235,11 +6278,11 @@
         <v>17</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>15</v>
+        <v>245</v>
       </c>
       <c r="M38" s="8"/>
     </row>
-    <row r="39" spans="2:13" ht="17.100000000000001">
+    <row r="39" spans="2:13" ht="33.950000000000003">
       <c r="B39" s="3">
         <v>36</v>
       </c>
@@ -6269,7 +6312,7 @@
         <v>17</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>15</v>
+        <v>246</v>
       </c>
       <c r="M39" s="8"/>
     </row>
@@ -6409,7 +6452,7 @@
         <v>17</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>15</v>
+        <v>247</v>
       </c>
       <c r="M43" s="8"/>
     </row>
@@ -6519,7 +6562,7 @@
       </c>
       <c r="M46" s="8"/>
     </row>
-    <row r="47" spans="2:13" ht="17.100000000000001">
+    <row r="47" spans="2:13" ht="51">
       <c r="B47" s="3">
         <v>44</v>
       </c>
@@ -6549,7 +6592,7 @@
         <v>17</v>
       </c>
       <c r="L47" s="9" t="s">
-        <v>15</v>
+        <v>248</v>
       </c>
       <c r="M47" s="8"/>
     </row>
@@ -6621,7 +6664,7 @@
       </c>
       <c r="M49" s="8"/>
     </row>
-    <row r="50" spans="2:13" ht="102">
+    <row r="50" spans="2:13" ht="84.95">
       <c r="B50" s="3">
         <v>47</v>
       </c>
@@ -6651,7 +6694,7 @@
         <v>17</v>
       </c>
       <c r="L50" s="9" t="s">
-        <v>185</v>
+        <v>249</v>
       </c>
       <c r="M50" s="8"/>
     </row>
@@ -6689,7 +6732,7 @@
       </c>
       <c r="M51" s="8"/>
     </row>
-    <row r="52" spans="2:13" ht="119.1">
+    <row r="52" spans="2:13" ht="135.94999999999999">
       <c r="B52" s="3">
         <v>49</v>
       </c>
@@ -6719,11 +6762,11 @@
         <v>17</v>
       </c>
       <c r="L52" s="9" t="s">
-        <v>189</v>
+        <v>250</v>
       </c>
       <c r="M52" s="8"/>
     </row>
-    <row r="53" spans="2:13" ht="17.100000000000001">
+    <row r="53" spans="2:13" ht="33.950000000000003">
       <c r="B53" s="3">
         <v>50</v>
       </c>
@@ -6753,7 +6796,7 @@
         <v>17</v>
       </c>
       <c r="L53" s="9" t="s">
-        <v>15</v>
+        <v>247</v>
       </c>
       <c r="M53" s="8"/>
     </row>
